--- a/discount_rules.xlsx
+++ b/discount_rules.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF398700-5FE7-4E9D-9AA3-16F09998F21B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF08ED2-53F9-47AA-9EA3-FE371DB8A921}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$I$347</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -9705,6 +9708,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I347" xr:uid="{06228357-5D49-4E60-80F1-A05F449BD87B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/discount_rules.xlsx
+++ b/discount_rules.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF08ED2-53F9-47AA-9EA3-FE371DB8A921}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4998D2AE-3846-4DEE-85AD-1FF2DC36AF6B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="113">
   <si>
     <t>level04</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>Увлажнители воздуха</t>
+  </si>
+  <si>
+    <t xml:space="preserve">До 5 см </t>
   </si>
 </sst>
 </file>
@@ -4036,7 +4039,7 @@
         <v>10</v>
       </c>
       <c r="H129">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
@@ -4050,7 +4053,7 @@
         <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="E130" t="s">
         <v>13</v>
@@ -4088,7 +4091,7 @@
         <v>15</v>
       </c>
       <c r="H131">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
@@ -9710,5 +9713,6 @@
   </sheetData>
   <autoFilter ref="A1:I347" xr:uid="{06228357-5D49-4E60-80F1-A05F449BD87B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>